--- a/excel_payment.xlsx
+++ b/excel_payment.xlsx
@@ -2,80 +2,113 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20384"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jackey\Desktop\github\work-order\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7816A198-266F-4FD0-B7D6-3C147CF938E6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{673A4432-E91A-46B5-8F03-DBA08163CF0F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="10133" xr2:uid="{81DCF461-78D8-4FC6-B330-283479D70F21}"/>
+    <workbookView showHorizontalScroll="0" showSheetTabs="0" xWindow="32767" yWindow="32767" windowWidth="24180" windowHeight="13053" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="報價單" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">報價單!$A$1:$M$30</definedName>
+  </definedNames>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="13">
-  <si>
-    <t>h93u4fu4;awlfuihawen;lfbjawl;fbkjawnpgf</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sergnergberg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>wefbwetnawe</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>awebawetbaw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>awetbawt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>awtbaw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bawetfgb</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>gbsergbsergbser</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sbergbsergbsergbserg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>egbsergbsergsergbsergbrgbsergbser</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bser</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bsrgb</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bsergb</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+  <si>
+    <t>彩意企業有限公司</t>
+  </si>
+  <si>
+    <t>新北市新店區富貴街23巷2號1樓
+TEL:(02)-22145786 FAX:(02)2214-5782</t>
+  </si>
+  <si>
+    <t>報價單</t>
+  </si>
+  <si>
+    <t>客戶名稱:</t>
+  </si>
+  <si>
+    <t>案件名稱:</t>
+  </si>
+  <si>
+    <t>連絡人員:</t>
+  </si>
+  <si>
+    <t>連絡電話:</t>
+  </si>
+  <si>
+    <t>客戶確認:</t>
+  </si>
+  <si>
+    <t>進場時間:</t>
+  </si>
+  <si>
+    <t>撤場時間:</t>
+  </si>
+  <si>
+    <t>施工地址:</t>
+  </si>
+  <si>
+    <t>公司地址:</t>
+  </si>
+  <si>
+    <t>製作項目</t>
+  </si>
+  <si>
+    <t>尺寸</t>
+  </si>
+  <si>
+    <t>數量</t>
+  </si>
+  <si>
+    <t>材質</t>
+  </si>
+  <si>
+    <t>板材種類</t>
+  </si>
+  <si>
+    <t>其他備料</t>
+  </si>
+  <si>
+    <t>才數</t>
+  </si>
+  <si>
+    <t>計價</t>
+  </si>
+  <si>
+    <t>特殊計價</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本報價單務必請承辦人員確認製作與製作金額後簽章並回本公司。
+本報價單請款方式為:於交貨日起算開立30日之內付款，務請貴公司配合請款條件，謝謝。
+</t>
+  </si>
+  <si>
+    <t>製作金額</t>
+  </si>
+  <si>
+    <t>稅額</t>
+  </si>
+  <si>
+    <t>製作總價</t>
+  </si>
+  <si>
+    <t>匯款資料:
+銀行:合作金庫-永吉分行(銀行代號006)
+帳號:0969-717-059213             戶名:彩意企業有限公司</t>
+  </si>
+  <si>
+    <t>公司統編:</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -83,24 +116,86 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_(&quot;￥&quot;* #,##0.00_);_(&quot;￥&quot;* \(#,##0.00\);_(&quot;￥&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="178" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);;_(@_)"/>
+    <numFmt numFmtId="179" formatCode="@\ \ "/>
+  </numFmts>
+  <fonts count="11">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="新細明體"/>
+      <sz val="10"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="新細明體"/>
+      <name val="細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="微軟正黑體"/>
       <family val="2"/>
       <charset val="136"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="36"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -109,36 +204,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFEBCD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFFFC0CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -146,30 +235,423 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="79">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-  </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -189,7 +671,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -205,7 +687,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -217,7 +699,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -231,12 +713,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -264,31 +746,14 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -316,23 +781,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -475,118 +923,547 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97AEA51B-33C4-497C-BBEC-8237BCCB4A14}">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="16.7" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:O38"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="12.7" zeroHeight="1"/>
   <cols>
-    <col min="1" max="1" width="36.41015625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.52734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1171875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.3515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.41015625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.3515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.17578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.3515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.46875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.234375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.234375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.234375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="11.64453125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="10.9375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="22.05859375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="24.52734375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="26.3515625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="19.1171875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.9375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="23.05859375" style="2" customWidth="1"/>
+    <col min="12" max="12" width="22.703125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="6.5859375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="9.1171875" style="2" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="0" style="2" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="9.1171875" style="2" hidden="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.1171875" style="2" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:13" ht="33.700000000000003" customHeight="1" thickBot="1">
+      <c r="B1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="L1" s="64"/>
+    </row>
+    <row r="2" spans="1:13" ht="17" customHeight="1">
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="64"/>
+    </row>
+    <row r="3" spans="1:13" ht="32.700000000000003" customHeight="1">
+      <c r="B3" s="46" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="50"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="G3" s="47"/>
+      <c r="H3" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="3"/>
+      <c r="J3" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" s="47"/>
+      <c r="L3" s="20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="32.700000000000003" customHeight="1">
+      <c r="B4" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="50"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I4" s="47"/>
+      <c r="J4" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K4" s="47"/>
+      <c r="L4" s="74"/>
+      <c r="M4" s="73"/>
+    </row>
+    <row r="5" spans="1:13" ht="33" customHeight="1">
+      <c r="B5" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="47"/>
+      <c r="D5" s="71" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="71"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="72"/>
+      <c r="K5" s="72"/>
+      <c r="L5" s="58"/>
+      <c r="M5" s="64"/>
+    </row>
+    <row r="6" spans="1:13" ht="30" customHeight="1">
+      <c r="A6" s="1"/>
+      <c r="B6" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="I1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="1"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="1"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="5"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="1"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="5"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="1"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="5"/>
-      <c r="H5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="1"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="5"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="C6" s="75" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="76"/>
+      <c r="E6" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="L6" s="21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="30" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="5"/>
-    </row>
+      <c r="B7" s="4"/>
+      <c r="C7" s="70"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="36"/>
+      <c r="L7" s="35"/>
+    </row>
+    <row r="8" spans="1:13" ht="30" customHeight="1">
+      <c r="A8" s="1"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="70"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="37"/>
+      <c r="J8" s="37"/>
+      <c r="K8" s="38"/>
+      <c r="L8" s="37"/>
+    </row>
+    <row r="9" spans="1:13" ht="30" customHeight="1">
+      <c r="A9" s="1"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="70"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="38"/>
+      <c r="L9" s="37"/>
+    </row>
+    <row r="10" spans="1:13" ht="30" customHeight="1">
+      <c r="A10" s="1"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="70"/>
+      <c r="D10" s="68"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="37"/>
+      <c r="I10" s="37"/>
+      <c r="J10" s="37"/>
+      <c r="K10" s="38"/>
+      <c r="L10" s="37"/>
+    </row>
+    <row r="11" spans="1:13" ht="30" customHeight="1">
+      <c r="A11" s="1"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="70"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="37"/>
+      <c r="H11" s="37"/>
+      <c r="I11" s="37"/>
+      <c r="J11" s="37"/>
+      <c r="K11" s="38"/>
+      <c r="L11" s="37"/>
+    </row>
+    <row r="12" spans="1:13" ht="30" customHeight="1">
+      <c r="A12" s="1"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="70"/>
+      <c r="D12" s="68"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="37"/>
+      <c r="H12" s="37"/>
+      <c r="I12" s="37"/>
+      <c r="J12" s="37"/>
+      <c r="K12" s="38"/>
+      <c r="L12" s="37"/>
+    </row>
+    <row r="13" spans="1:13" ht="30" customHeight="1">
+      <c r="A13" s="1"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="70"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="35"/>
+      <c r="K13" s="36"/>
+      <c r="L13" s="35"/>
+    </row>
+    <row r="14" spans="1:13" ht="30" customHeight="1">
+      <c r="A14" s="1"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="70"/>
+      <c r="D14" s="68"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="6"/>
+    </row>
+    <row r="15" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1">
+      <c r="B15" s="5"/>
+      <c r="C15" s="70"/>
+      <c r="D15" s="68"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="40"/>
+      <c r="K15" s="41"/>
+      <c r="L15" s="40"/>
+    </row>
+    <row r="16" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1">
+      <c r="B16" s="5"/>
+      <c r="C16" s="70"/>
+      <c r="D16" s="68"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="41"/>
+      <c r="L16" s="40"/>
+    </row>
+    <row r="17" spans="1:12" ht="30" customHeight="1">
+      <c r="A17" s="1"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="70"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="44"/>
+      <c r="L17" s="43"/>
+    </row>
+    <row r="18" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
+      <c r="B18" s="7"/>
+      <c r="C18" s="67"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="7"/>
+    </row>
+    <row r="19" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
+      <c r="B19" s="7"/>
+      <c r="C19" s="67"/>
+      <c r="D19" s="68"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="8"/>
+    </row>
+    <row r="20" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
+      <c r="B20" s="7"/>
+      <c r="C20" s="67"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="7"/>
+    </row>
+    <row r="21" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
+      <c r="B21" s="15"/>
+      <c r="C21" s="69"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="31"/>
+      <c r="L21" s="10"/>
+    </row>
+    <row r="22" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
+      <c r="B22" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="55"/>
+      <c r="G22" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="H22" s="16"/>
+      <c r="I22" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="J22" s="16"/>
+      <c r="K22" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="17"/>
+    </row>
+    <row r="23" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
+      <c r="B23" s="56"/>
+      <c r="C23" s="57"/>
+      <c r="D23" s="57"/>
+      <c r="E23" s="57"/>
+      <c r="F23" s="58"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="78"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="54"/>
+      <c r="K23" s="54"/>
+      <c r="L23" s="55"/>
+    </row>
+    <row r="24" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
+      <c r="B24" s="59" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="54"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="55"/>
+      <c r="H24" s="60"/>
+      <c r="I24" s="61"/>
+      <c r="J24" s="61"/>
+      <c r="K24" s="61"/>
+      <c r="L24" s="62"/>
+    </row>
+    <row r="25" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
+      <c r="B25" s="60"/>
+      <c r="C25" s="61"/>
+      <c r="D25" s="61"/>
+      <c r="E25" s="61"/>
+      <c r="F25" s="61"/>
+      <c r="G25" s="62"/>
+      <c r="H25" s="60"/>
+      <c r="I25" s="61"/>
+      <c r="J25" s="61"/>
+      <c r="K25" s="61"/>
+      <c r="L25" s="62"/>
+    </row>
+    <row r="26" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
+      <c r="B26" s="60"/>
+      <c r="C26" s="61"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="61"/>
+      <c r="F26" s="61"/>
+      <c r="G26" s="62"/>
+      <c r="H26" s="60"/>
+      <c r="I26" s="61"/>
+      <c r="J26" s="61"/>
+      <c r="K26" s="61"/>
+      <c r="L26" s="62"/>
+    </row>
+    <row r="27" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
+      <c r="B27" s="60"/>
+      <c r="C27" s="61"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="61"/>
+      <c r="F27" s="61"/>
+      <c r="G27" s="62"/>
+      <c r="H27" s="60"/>
+      <c r="I27" s="61"/>
+      <c r="J27" s="61"/>
+      <c r="K27" s="61"/>
+      <c r="L27" s="62"/>
+    </row>
+    <row r="28" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
+      <c r="B28" s="60"/>
+      <c r="C28" s="61"/>
+      <c r="D28" s="61"/>
+      <c r="E28" s="61"/>
+      <c r="F28" s="61"/>
+      <c r="G28" s="62"/>
+      <c r="H28" s="60"/>
+      <c r="I28" s="61"/>
+      <c r="J28" s="61"/>
+      <c r="K28" s="61"/>
+      <c r="L28" s="62"/>
+    </row>
+    <row r="29" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
+      <c r="B29" s="56"/>
+      <c r="C29" s="57"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="57"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="58"/>
+      <c r="H29" s="56"/>
+      <c r="I29" s="57"/>
+      <c r="J29" s="57"/>
+      <c r="K29" s="57"/>
+      <c r="L29" s="58"/>
+    </row>
+    <row r="30" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="14"/>
+    </row>
+    <row r="31" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="32"/>
+      <c r="J31" s="32"/>
+      <c r="K31" s="32"/>
+      <c r="L31" s="32"/>
+    </row>
+    <row r="32" spans="1:12" s="1" customFormat="1" ht="23.35" customHeight="1">
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+    </row>
+    <row r="33" s="1" customFormat="1"/>
+    <row r="38"/>
   </sheetData>
+  <mergeCells count="28">
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="K1:L2"/>
+    <mergeCell ref="H23:L29"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="B22:F23"/>
+    <mergeCell ref="B24:G29"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="F1:J2"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:K5"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0" right="0" top="0.59055118110236227" bottom="0.19685039370078741" header="0.31496062992125978" footer="0.31496062992125978"/>
+  <pageSetup paperSize="9" scale="64" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/excel_payment.xlsx
+++ b/excel_payment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jackey\Desktop\github\work-order\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{673A4432-E91A-46B5-8F03-DBA08163CF0F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12425053-1578-493C-A072-AF9D56FC9BC6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView showHorizontalScroll="0" showSheetTabs="0" xWindow="32767" yWindow="32767" windowWidth="24180" windowHeight="13053" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -123,7 +123,7 @@
     <numFmt numFmtId="178" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);;_(@_)"/>
     <numFmt numFmtId="179" formatCode="@\ \ "/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -194,6 +194,12 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="22"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -459,7 +465,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -590,15 +596,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -652,6 +650,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -938,10 +945,10 @@
     <col min="2" max="2" width="20.234375" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.234375" style="2" customWidth="1"/>
     <col min="4" max="4" width="11.64453125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="10.9375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="22.05859375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="24.52734375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="26.3515625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.64453125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="19.1171875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="44.5859375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="27.41015625" style="2" customWidth="1"/>
     <col min="9" max="9" width="19.1171875" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19.9375" style="2" customWidth="1"/>
     <col min="11" max="11" width="23.05859375" style="2" customWidth="1"/>
@@ -954,48 +961,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="33.700000000000003" customHeight="1" thickBot="1">
-      <c r="B1" s="63" t="s">
+      <c r="B1" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
       <c r="E1" s="29"/>
-      <c r="F1" s="66" t="s">
+      <c r="F1" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="77" t="s">
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="64"/>
+      <c r="L1" s="62"/>
     </row>
     <row r="2" spans="1:13" ht="17" customHeight="1">
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
       <c r="E2" s="45"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="64"/>
-      <c r="L2" s="64"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="62"/>
+      <c r="L2" s="62"/>
     </row>
     <row r="3" spans="1:13" ht="32.700000000000003" customHeight="1">
       <c r="B3" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="52"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="79"/>
       <c r="F3" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="47"/>
+      <c r="G3" s="50"/>
       <c r="H3" s="46" t="s">
         <v>5</v>
       </c>
@@ -1012,11 +1019,11 @@
       <c r="B4" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="50"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="52"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="79"/>
       <c r="H4" s="49" t="s">
         <v>8</v>
       </c>
@@ -1025,36 +1032,36 @@
         <v>9</v>
       </c>
       <c r="K4" s="47"/>
-      <c r="L4" s="74"/>
-      <c r="M4" s="73"/>
+      <c r="L4" s="72"/>
+      <c r="M4" s="71"/>
     </row>
     <row r="5" spans="1:13" ht="33" customHeight="1">
       <c r="B5" s="46" t="s">
         <v>26</v>
       </c>
       <c r="C5" s="47"/>
-      <c r="D5" s="71" t="s">
+      <c r="D5" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="71"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="72"/>
-      <c r="I5" s="72"/>
-      <c r="J5" s="72"/>
-      <c r="K5" s="72"/>
-      <c r="L5" s="58"/>
-      <c r="M5" s="64"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="70"/>
+      <c r="K5" s="70"/>
+      <c r="L5" s="56"/>
+      <c r="M5" s="62"/>
     </row>
     <row r="6" spans="1:13" ht="30" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="75" t="s">
+      <c r="C6" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="76"/>
+      <c r="D6" s="74"/>
       <c r="E6" s="25" t="s">
         <v>14</v>
       </c>
@@ -1083,8 +1090,8 @@
     <row r="7" spans="1:13" ht="30" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="4"/>
-      <c r="C7" s="70"/>
-      <c r="D7" s="68"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="66"/>
       <c r="E7" s="4"/>
       <c r="F7" s="33"/>
       <c r="G7" s="34"/>
@@ -1097,8 +1104,8 @@
     <row r="8" spans="1:13" ht="30" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="4"/>
-      <c r="C8" s="70"/>
-      <c r="D8" s="68"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="66"/>
       <c r="E8" s="4"/>
       <c r="F8" s="33"/>
       <c r="G8" s="37"/>
@@ -1111,8 +1118,8 @@
     <row r="9" spans="1:13" ht="30" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="4"/>
-      <c r="C9" s="70"/>
-      <c r="D9" s="68"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="66"/>
       <c r="E9" s="4"/>
       <c r="F9" s="33"/>
       <c r="G9" s="37"/>
@@ -1125,8 +1132,8 @@
     <row r="10" spans="1:13" ht="30" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="4"/>
-      <c r="C10" s="70"/>
-      <c r="D10" s="68"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="66"/>
       <c r="E10" s="4"/>
       <c r="F10" s="33"/>
       <c r="G10" s="37"/>
@@ -1139,8 +1146,8 @@
     <row r="11" spans="1:13" ht="30" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="4"/>
-      <c r="C11" s="70"/>
-      <c r="D11" s="68"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="66"/>
       <c r="E11" s="4"/>
       <c r="F11" s="33"/>
       <c r="G11" s="37"/>
@@ -1153,8 +1160,8 @@
     <row r="12" spans="1:13" ht="30" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="4"/>
-      <c r="C12" s="70"/>
-      <c r="D12" s="68"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="66"/>
       <c r="E12" s="4"/>
       <c r="F12" s="33"/>
       <c r="G12" s="37"/>
@@ -1167,8 +1174,8 @@
     <row r="13" spans="1:13" ht="30" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="5"/>
-      <c r="C13" s="70"/>
-      <c r="D13" s="68"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="66"/>
       <c r="E13" s="5"/>
       <c r="F13" s="4"/>
       <c r="G13" s="39"/>
@@ -1181,8 +1188,8 @@
     <row r="14" spans="1:13" ht="30" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="5"/>
-      <c r="C14" s="70"/>
-      <c r="D14" s="68"/>
+      <c r="C14" s="68"/>
+      <c r="D14" s="66"/>
       <c r="E14" s="5"/>
       <c r="F14" s="4"/>
       <c r="G14" s="39"/>
@@ -1194,8 +1201,8 @@
     </row>
     <row r="15" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B15" s="5"/>
-      <c r="C15" s="70"/>
-      <c r="D15" s="68"/>
+      <c r="C15" s="68"/>
+      <c r="D15" s="66"/>
       <c r="E15" s="5"/>
       <c r="F15" s="4"/>
       <c r="G15" s="39"/>
@@ -1207,8 +1214,8 @@
     </row>
     <row r="16" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B16" s="5"/>
-      <c r="C16" s="70"/>
-      <c r="D16" s="68"/>
+      <c r="C16" s="68"/>
+      <c r="D16" s="66"/>
       <c r="E16" s="5"/>
       <c r="F16" s="4"/>
       <c r="G16" s="39"/>
@@ -1221,8 +1228,8 @@
     <row r="17" spans="1:12" ht="30" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="4"/>
-      <c r="C17" s="70"/>
-      <c r="D17" s="68"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="66"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="42"/>
@@ -1234,8 +1241,8 @@
     </row>
     <row r="18" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B18" s="7"/>
-      <c r="C18" s="67"/>
-      <c r="D18" s="68"/>
+      <c r="C18" s="65"/>
+      <c r="D18" s="66"/>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
@@ -1247,8 +1254,8 @@
     </row>
     <row r="19" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B19" s="7"/>
-      <c r="C19" s="67"/>
-      <c r="D19" s="68"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="66"/>
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
@@ -1260,8 +1267,8 @@
     </row>
     <row r="20" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B20" s="7"/>
-      <c r="C20" s="67"/>
-      <c r="D20" s="68"/>
+      <c r="C20" s="65"/>
+      <c r="D20" s="66"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
@@ -1273,8 +1280,8 @@
     </row>
     <row r="21" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B21" s="15"/>
-      <c r="C21" s="69"/>
-      <c r="D21" s="68"/>
+      <c r="C21" s="67"/>
+      <c r="D21" s="66"/>
       <c r="E21" s="15"/>
       <c r="F21" s="15"/>
       <c r="G21" s="9"/>
@@ -1285,13 +1292,13 @@
       <c r="L21" s="10"/>
     </row>
     <row r="22" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="B22" s="53" t="s">
+      <c r="B22" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="54"/>
-      <c r="D22" s="54"/>
-      <c r="E22" s="54"/>
-      <c r="F22" s="55"/>
+      <c r="C22" s="52"/>
+      <c r="D22" s="52"/>
+      <c r="E22" s="52"/>
+      <c r="F22" s="53"/>
       <c r="G22" s="22" t="s">
         <v>22</v>
       </c>
@@ -1306,97 +1313,97 @@
       <c r="L22" s="17"/>
     </row>
     <row r="23" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="B23" s="56"/>
-      <c r="C23" s="57"/>
-      <c r="D23" s="57"/>
-      <c r="E23" s="57"/>
-      <c r="F23" s="58"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="55"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="55"/>
+      <c r="F23" s="56"/>
       <c r="G23" s="18"/>
-      <c r="H23" s="78"/>
-      <c r="I23" s="54"/>
-      <c r="J23" s="54"/>
-      <c r="K23" s="54"/>
-      <c r="L23" s="55"/>
+      <c r="H23" s="76"/>
+      <c r="I23" s="52"/>
+      <c r="J23" s="52"/>
+      <c r="K23" s="52"/>
+      <c r="L23" s="53"/>
     </row>
     <row r="24" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
-      <c r="B24" s="59" t="s">
+      <c r="B24" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="54"/>
-      <c r="D24" s="54"/>
-      <c r="E24" s="54"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="55"/>
-      <c r="H24" s="60"/>
-      <c r="I24" s="61"/>
-      <c r="J24" s="61"/>
-      <c r="K24" s="61"/>
-      <c r="L24" s="62"/>
+      <c r="C24" s="52"/>
+      <c r="D24" s="52"/>
+      <c r="E24" s="52"/>
+      <c r="F24" s="52"/>
+      <c r="G24" s="53"/>
+      <c r="H24" s="58"/>
+      <c r="I24" s="59"/>
+      <c r="J24" s="59"/>
+      <c r="K24" s="59"/>
+      <c r="L24" s="60"/>
     </row>
     <row r="25" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
-      <c r="B25" s="60"/>
-      <c r="C25" s="61"/>
-      <c r="D25" s="61"/>
-      <c r="E25" s="61"/>
-      <c r="F25" s="61"/>
-      <c r="G25" s="62"/>
-      <c r="H25" s="60"/>
-      <c r="I25" s="61"/>
-      <c r="J25" s="61"/>
-      <c r="K25" s="61"/>
-      <c r="L25" s="62"/>
+      <c r="B25" s="58"/>
+      <c r="C25" s="59"/>
+      <c r="D25" s="59"/>
+      <c r="E25" s="59"/>
+      <c r="F25" s="59"/>
+      <c r="G25" s="60"/>
+      <c r="H25" s="58"/>
+      <c r="I25" s="59"/>
+      <c r="J25" s="59"/>
+      <c r="K25" s="59"/>
+      <c r="L25" s="60"/>
     </row>
     <row r="26" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
-      <c r="B26" s="60"/>
-      <c r="C26" s="61"/>
-      <c r="D26" s="61"/>
-      <c r="E26" s="61"/>
-      <c r="F26" s="61"/>
-      <c r="G26" s="62"/>
-      <c r="H26" s="60"/>
-      <c r="I26" s="61"/>
-      <c r="J26" s="61"/>
-      <c r="K26" s="61"/>
-      <c r="L26" s="62"/>
+      <c r="B26" s="58"/>
+      <c r="C26" s="59"/>
+      <c r="D26" s="59"/>
+      <c r="E26" s="59"/>
+      <c r="F26" s="59"/>
+      <c r="G26" s="60"/>
+      <c r="H26" s="58"/>
+      <c r="I26" s="59"/>
+      <c r="J26" s="59"/>
+      <c r="K26" s="59"/>
+      <c r="L26" s="60"/>
     </row>
     <row r="27" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
-      <c r="B27" s="60"/>
-      <c r="C27" s="61"/>
-      <c r="D27" s="61"/>
-      <c r="E27" s="61"/>
-      <c r="F27" s="61"/>
-      <c r="G27" s="62"/>
-      <c r="H27" s="60"/>
-      <c r="I27" s="61"/>
-      <c r="J27" s="61"/>
-      <c r="K27" s="61"/>
-      <c r="L27" s="62"/>
+      <c r="B27" s="58"/>
+      <c r="C27" s="59"/>
+      <c r="D27" s="59"/>
+      <c r="E27" s="59"/>
+      <c r="F27" s="59"/>
+      <c r="G27" s="60"/>
+      <c r="H27" s="58"/>
+      <c r="I27" s="59"/>
+      <c r="J27" s="59"/>
+      <c r="K27" s="59"/>
+      <c r="L27" s="60"/>
     </row>
     <row r="28" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
-      <c r="B28" s="60"/>
-      <c r="C28" s="61"/>
-      <c r="D28" s="61"/>
-      <c r="E28" s="61"/>
-      <c r="F28" s="61"/>
-      <c r="G28" s="62"/>
-      <c r="H28" s="60"/>
-      <c r="I28" s="61"/>
-      <c r="J28" s="61"/>
-      <c r="K28" s="61"/>
-      <c r="L28" s="62"/>
+      <c r="B28" s="58"/>
+      <c r="C28" s="59"/>
+      <c r="D28" s="59"/>
+      <c r="E28" s="59"/>
+      <c r="F28" s="59"/>
+      <c r="G28" s="60"/>
+      <c r="H28" s="58"/>
+      <c r="I28" s="59"/>
+      <c r="J28" s="59"/>
+      <c r="K28" s="59"/>
+      <c r="L28" s="60"/>
     </row>
     <row r="29" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
-      <c r="B29" s="56"/>
-      <c r="C29" s="57"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="57"/>
-      <c r="F29" s="57"/>
-      <c r="G29" s="58"/>
-      <c r="H29" s="56"/>
-      <c r="I29" s="57"/>
-      <c r="J29" s="57"/>
-      <c r="K29" s="57"/>
-      <c r="L29" s="58"/>
+      <c r="B29" s="54"/>
+      <c r="C29" s="55"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="55"/>
+      <c r="F29" s="55"/>
+      <c r="G29" s="56"/>
+      <c r="H29" s="54"/>
+      <c r="I29" s="55"/>
+      <c r="J29" s="55"/>
+      <c r="K29" s="55"/>
+      <c r="L29" s="56"/>
     </row>
     <row r="30" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
       <c r="B30" s="19"/>
@@ -1464,6 +1471,6 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.59055118110236227" bottom="0.19685039370078741" header="0.31496062992125978" footer="0.31496062992125978"/>
-  <pageSetup paperSize="9" scale="64" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="58" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/excel_payment.xlsx
+++ b/excel_payment.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jackey\Desktop\github\work-order\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jackey\Desktop\github\work-order\app\dist\main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F955BDC1-2304-4902-B594-21E6B853B22A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBEEE61B-8B44-4017-BE05-03A93134ACBE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView showHorizontalScroll="0" showSheetTabs="0" xWindow="32767" yWindow="32767" windowWidth="24180" windowHeight="13053" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>彩意企業有限公司</t>
   </si>
@@ -109,10 +109,6 @@
   </si>
   <si>
     <t>公司統編:</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>備料數量</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -120,7 +116,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -190,13 +186,6 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
-    <font>
-      <sz val="22"/>
-      <name val="新細明體"/>
-      <family val="1"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -519,23 +508,28 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
@@ -543,9 +537,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -555,34 +576,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -864,15 +857,15 @@
   <dimension ref="A1:O38"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="12.7" zeroHeight="1"/>
   <cols>
-    <col min="1" max="1" width="5.234375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.234375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.234375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="14.29296875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.64453125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="19.1171875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="44.5859375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="27.41015625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="20.41015625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="4.9375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="36.3515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.17578125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="5.8203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="22" style="2" customWidth="1"/>
+    <col min="6" max="6" width="21.46875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="31.5859375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="23.46875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="18.52734375" style="2" customWidth="1"/>
     <col min="10" max="10" width="19.9375" style="2" customWidth="1"/>
     <col min="11" max="11" width="23.05859375" style="2" customWidth="1"/>
     <col min="12" max="12" width="22.703125" style="2" customWidth="1"/>
@@ -884,48 +877,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="33.700000000000003" customHeight="1" thickBot="1">
-      <c r="B1" s="43" t="s">
+      <c r="B1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
       <c r="E1" s="17"/>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="30" t="s">
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="27"/>
+      <c r="L1" s="40"/>
     </row>
     <row r="2" spans="1:13" ht="17" customHeight="1">
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
       <c r="E2" s="20"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
     </row>
     <row r="3" spans="1:13" ht="32.700000000000003" customHeight="1">
       <c r="B3" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="23" t="s">
+      <c r="C3" s="51"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="25"/>
+      <c r="G3" s="24"/>
       <c r="H3" s="21" t="s">
         <v>5</v>
       </c>
@@ -942,12 +935,12 @@
       <c r="B4" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="39"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="24" t="s">
+      <c r="C4" s="51"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="23" t="s">
         <v>8</v>
       </c>
       <c r="I4" s="22"/>
@@ -955,36 +948,36 @@
         <v>9</v>
       </c>
       <c r="K4" s="22"/>
-      <c r="L4" s="28"/>
-      <c r="M4" s="26"/>
+      <c r="L4" s="46"/>
+      <c r="M4" s="45"/>
     </row>
     <row r="5" spans="1:13" ht="33" customHeight="1">
       <c r="B5" s="21" t="s">
         <v>26</v>
       </c>
       <c r="C5" s="22"/>
-      <c r="D5" s="46" t="s">
+      <c r="D5" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="46"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="47"/>
-      <c r="I5" s="47"/>
-      <c r="J5" s="47"/>
-      <c r="K5" s="47"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="27"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="44"/>
+      <c r="K5" s="44"/>
+      <c r="L5" s="33"/>
+      <c r="M5" s="40"/>
     </row>
     <row r="6" spans="1:13" ht="30" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="48" t="s">
+      <c r="C6" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="49"/>
+      <c r="D6" s="48"/>
       <c r="E6" s="13" t="s">
         <v>14</v>
       </c>
@@ -998,7 +991,7 @@
         <v>17</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="J6" s="15" t="s">
         <v>18</v>
@@ -1006,222 +999,222 @@
       <c r="K6" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="L6" s="50" t="s">
+      <c r="L6" s="25" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="30" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="52"/>
-      <c r="C7" s="53"/>
-      <c r="D7" s="53"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
-      <c r="J7" s="52"/>
-      <c r="K7" s="52"/>
-      <c r="L7" s="52"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="26"/>
     </row>
     <row r="8" spans="1:13" ht="30" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="52"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="52"/>
-      <c r="K8" s="52"/>
-      <c r="L8" s="52"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="26"/>
     </row>
     <row r="9" spans="1:13" ht="30" customHeight="1">
       <c r="A9" s="1"/>
-      <c r="B9" s="52"/>
-      <c r="C9" s="53"/>
-      <c r="D9" s="53"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="52"/>
-      <c r="K9" s="52"/>
-      <c r="L9" s="52"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="26"/>
     </row>
     <row r="10" spans="1:13" ht="30" customHeight="1">
       <c r="A10" s="1"/>
-      <c r="B10" s="52"/>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="52"/>
-      <c r="K10" s="52"/>
-      <c r="L10" s="52"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
     </row>
     <row r="11" spans="1:13" ht="30" customHeight="1">
       <c r="A11" s="1"/>
-      <c r="B11" s="52"/>
-      <c r="C11" s="53"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="52"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="52"/>
-      <c r="K11" s="52"/>
-      <c r="L11" s="52"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="26"/>
     </row>
     <row r="12" spans="1:13" ht="30" customHeight="1">
       <c r="A12" s="1"/>
-      <c r="B12" s="52"/>
-      <c r="C12" s="53"/>
-      <c r="D12" s="53"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="52"/>
-      <c r="K12" s="52"/>
-      <c r="L12" s="52"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="26"/>
     </row>
     <row r="13" spans="1:13" ht="30" customHeight="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="52"/>
-      <c r="C13" s="53"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="52"/>
-      <c r="K13" s="52"/>
-      <c r="L13" s="52"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
+      <c r="L13" s="26"/>
     </row>
     <row r="14" spans="1:13" ht="30" customHeight="1">
       <c r="A14" s="1"/>
-      <c r="B14" s="52"/>
-      <c r="C14" s="53"/>
-      <c r="D14" s="53"/>
-      <c r="E14" s="52"/>
-      <c r="F14" s="52"/>
-      <c r="G14" s="52"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="52"/>
-      <c r="K14" s="52"/>
-      <c r="L14" s="52"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
+      <c r="L14" s="26"/>
     </row>
     <row r="15" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="B15" s="52"/>
-      <c r="C15" s="53"/>
-      <c r="D15" s="53"/>
-      <c r="E15" s="52"/>
-      <c r="F15" s="52"/>
-      <c r="G15" s="52"/>
-      <c r="H15" s="52"/>
-      <c r="I15" s="52"/>
-      <c r="J15" s="52"/>
-      <c r="K15" s="52"/>
-      <c r="L15" s="52"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="26"/>
+      <c r="L15" s="26"/>
     </row>
     <row r="16" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="B16" s="52"/>
-      <c r="C16" s="53"/>
-      <c r="D16" s="53"/>
-      <c r="E16" s="52"/>
-      <c r="F16" s="52"/>
-      <c r="G16" s="52"/>
-      <c r="H16" s="52"/>
-      <c r="I16" s="52"/>
-      <c r="J16" s="52"/>
-      <c r="K16" s="52"/>
-      <c r="L16" s="52"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="26"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="26"/>
     </row>
     <row r="17" spans="1:12" ht="30" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="52"/>
-      <c r="C17" s="53"/>
-      <c r="D17" s="53"/>
-      <c r="E17" s="52"/>
-      <c r="F17" s="52"/>
-      <c r="G17" s="52"/>
-      <c r="H17" s="52"/>
-      <c r="I17" s="52"/>
-      <c r="J17" s="52"/>
-      <c r="K17" s="52"/>
-      <c r="L17" s="52"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="26"/>
+      <c r="K17" s="26"/>
+      <c r="L17" s="26"/>
     </row>
     <row r="18" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="B18" s="52"/>
-      <c r="C18" s="53"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="52"/>
-      <c r="F18" s="52"/>
-      <c r="G18" s="52"/>
-      <c r="H18" s="52"/>
-      <c r="I18" s="52"/>
-      <c r="J18" s="52"/>
-      <c r="K18" s="52"/>
-      <c r="L18" s="52"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="26"/>
+      <c r="K18" s="26"/>
+      <c r="L18" s="26"/>
     </row>
     <row r="19" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="B19" s="52"/>
-      <c r="C19" s="53"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="52"/>
-      <c r="F19" s="52"/>
-      <c r="G19" s="52"/>
-      <c r="H19" s="52"/>
-      <c r="I19" s="52"/>
-      <c r="J19" s="52"/>
-      <c r="K19" s="52"/>
-      <c r="L19" s="52"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="26"/>
+      <c r="K19" s="26"/>
+      <c r="L19" s="26"/>
     </row>
     <row r="20" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="B20" s="52"/>
-      <c r="C20" s="53"/>
-      <c r="D20" s="53"/>
-      <c r="E20" s="52"/>
-      <c r="F20" s="52"/>
-      <c r="G20" s="52"/>
-      <c r="H20" s="52"/>
-      <c r="I20" s="52"/>
-      <c r="J20" s="52"/>
-      <c r="K20" s="52"/>
-      <c r="L20" s="52"/>
+      <c r="B20" s="26"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="26"/>
+      <c r="K20" s="26"/>
+      <c r="L20" s="26"/>
     </row>
     <row r="21" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="B21" s="52"/>
-      <c r="C21" s="53"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="52"/>
-      <c r="F21" s="52"/>
-      <c r="G21" s="52"/>
-      <c r="H21" s="52"/>
-      <c r="I21" s="52"/>
-      <c r="J21" s="52"/>
-      <c r="K21" s="52"/>
-      <c r="L21" s="52"/>
+      <c r="B21" s="26"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="26"/>
+      <c r="J21" s="26"/>
+      <c r="K21" s="26"/>
+      <c r="L21" s="26"/>
     </row>
     <row r="22" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="B22" s="51" t="s">
+      <c r="B22" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="44"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="44"/>
-      <c r="F22" s="36"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="30"/>
       <c r="G22" s="10" t="s">
         <v>22</v>
       </c>
@@ -1236,97 +1229,97 @@
       <c r="L22" s="6"/>
     </row>
     <row r="23" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="B23" s="37"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="29"/>
+      <c r="B23" s="31"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="33"/>
       <c r="G23" s="7"/>
-      <c r="H23" s="31"/>
-      <c r="I23" s="32"/>
-      <c r="J23" s="32"/>
-      <c r="K23" s="32"/>
-      <c r="L23" s="33"/>
+      <c r="H23" s="50"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="35"/>
+      <c r="K23" s="35"/>
+      <c r="L23" s="36"/>
     </row>
     <row r="24" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
-      <c r="B24" s="42" t="s">
+      <c r="B24" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="32"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="32"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="33"/>
-      <c r="H24" s="34"/>
-      <c r="I24" s="35"/>
-      <c r="J24" s="35"/>
-      <c r="K24" s="35"/>
-      <c r="L24" s="36"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="37"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="38"/>
+      <c r="L24" s="30"/>
     </row>
     <row r="25" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
-      <c r="B25" s="34"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="34"/>
-      <c r="I25" s="35"/>
-      <c r="J25" s="35"/>
-      <c r="K25" s="35"/>
-      <c r="L25" s="36"/>
+      <c r="B25" s="37"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="37"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="38"/>
+      <c r="L25" s="30"/>
     </row>
     <row r="26" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
-      <c r="B26" s="34"/>
-      <c r="C26" s="35"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="36"/>
-      <c r="H26" s="34"/>
-      <c r="I26" s="35"/>
-      <c r="J26" s="35"/>
-      <c r="K26" s="35"/>
-      <c r="L26" s="36"/>
+      <c r="B26" s="37"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="37"/>
+      <c r="I26" s="38"/>
+      <c r="J26" s="38"/>
+      <c r="K26" s="38"/>
+      <c r="L26" s="30"/>
     </row>
     <row r="27" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
-      <c r="B27" s="34"/>
-      <c r="C27" s="35"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="36"/>
-      <c r="H27" s="34"/>
-      <c r="I27" s="35"/>
-      <c r="J27" s="35"/>
-      <c r="K27" s="35"/>
-      <c r="L27" s="36"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="38"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="37"/>
+      <c r="I27" s="38"/>
+      <c r="J27" s="38"/>
+      <c r="K27" s="38"/>
+      <c r="L27" s="30"/>
     </row>
     <row r="28" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
-      <c r="B28" s="34"/>
-      <c r="C28" s="35"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="35"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="36"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="35"/>
-      <c r="J28" s="35"/>
-      <c r="K28" s="35"/>
-      <c r="L28" s="36"/>
+      <c r="B28" s="37"/>
+      <c r="C28" s="38"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="37"/>
+      <c r="I28" s="38"/>
+      <c r="J28" s="38"/>
+      <c r="K28" s="38"/>
+      <c r="L28" s="30"/>
     </row>
     <row r="29" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
-      <c r="B29" s="37"/>
-      <c r="C29" s="38"/>
-      <c r="D29" s="38"/>
-      <c r="E29" s="38"/>
-      <c r="F29" s="38"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="37"/>
-      <c r="I29" s="38"/>
-      <c r="J29" s="38"/>
-      <c r="K29" s="38"/>
-      <c r="L29" s="29"/>
+      <c r="B29" s="31"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="33"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="32"/>
+      <c r="J29" s="32"/>
+      <c r="K29" s="32"/>
+      <c r="L29" s="33"/>
     </row>
     <row r="30" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
       <c r="B30" s="8"/>
@@ -1362,18 +1355,6 @@
     <row r="38"/>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B22:F23"/>
-    <mergeCell ref="B24:G29"/>
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="F1:J2"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:K5"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="C6:D6"/>
@@ -1390,6 +1371,18 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="C3:E3"/>
+    <mergeCell ref="B22:F23"/>
+    <mergeCell ref="B24:G29"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="F1:J2"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:K5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/excel_payment.xlsx
+++ b/excel_payment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20386"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20388"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jackey\Desktop\github\work-order\app\dist\main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jackey\Desktop\github\work-order\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBEEE61B-8B44-4017-BE05-03A93134ACBE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3177E884-5B65-41FC-B465-33C7D71D0C12}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView showHorizontalScroll="0" showSheetTabs="0" xWindow="32767" yWindow="32767" windowWidth="24180" windowHeight="13053" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -86,29 +86,31 @@
     <t>計價</t>
   </si>
   <si>
-    <t>特殊計價</t>
+    <t>製作金額</t>
+  </si>
+  <si>
+    <t>稅額</t>
+  </si>
+  <si>
+    <t>製作總價</t>
+  </si>
+  <si>
+    <t>匯款資料:
+銀行:合作金庫-永吉分行(銀行代號006)
+帳號:0969-717-059213             戶名:彩意企業有限公司</t>
+  </si>
+  <si>
+    <t>公司統編:</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">本報價單務必請承辦人員確認製作與製作金額後簽章並回本公司。
 本報價單請款方式為:於交貨日起算開立30日之內付款，務請貴公司配合請款條件，謝謝。
 </t>
-  </si>
-  <si>
-    <t>製作金額</t>
-  </si>
-  <si>
-    <t>稅額</t>
-  </si>
-  <si>
-    <t>製作總價</t>
-  </si>
-  <si>
-    <t>匯款資料:
-銀行:合作金庫-永吉分行(銀行代號006)
-帳號:0969-717-059213             戶名:彩意企業有限公司</t>
-  </si>
-  <si>
-    <t>公司統編:</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>備料計價</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -520,16 +522,21 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
@@ -537,43 +544,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -877,44 +879,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="33.700000000000003" customHeight="1" thickBot="1">
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
       <c r="E1" s="17"/>
-      <c r="F1" s="41" t="s">
+      <c r="F1" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="49" t="s">
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="40"/>
+      <c r="L1" s="29"/>
     </row>
     <row r="2" spans="1:13" ht="17" customHeight="1">
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
       <c r="E2" s="20"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
     </row>
     <row r="3" spans="1:13" ht="32.700000000000003" customHeight="1">
       <c r="B3" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="53"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="46"/>
       <c r="F3" s="27" t="s">
         <v>4</v>
       </c>
@@ -935,11 +937,11 @@
       <c r="B4" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="51"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="53"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="46"/>
       <c r="H4" s="23" t="s">
         <v>8</v>
       </c>
@@ -948,36 +950,36 @@
         <v>9</v>
       </c>
       <c r="K4" s="22"/>
-      <c r="L4" s="46"/>
-      <c r="M4" s="45"/>
+      <c r="L4" s="30"/>
+      <c r="M4" s="28"/>
     </row>
     <row r="5" spans="1:13" ht="33" customHeight="1">
       <c r="B5" s="21" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C5" s="22"/>
-      <c r="D5" s="43" t="s">
+      <c r="D5" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="43"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="44"/>
-      <c r="K5" s="44"/>
-      <c r="L5" s="33"/>
-      <c r="M5" s="40"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="53"/>
+      <c r="K5" s="53"/>
+      <c r="L5" s="31"/>
+      <c r="M5" s="29"/>
     </row>
     <row r="6" spans="1:13" ht="30" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="47" t="s">
+      <c r="C6" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="48"/>
+      <c r="D6" s="33"/>
       <c r="E6" s="13" t="s">
         <v>14</v>
       </c>
@@ -1000,14 +1002,14 @@
         <v>19</v>
       </c>
       <c r="L6" s="25" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="30" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="26"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
       <c r="G7" s="26"/>
@@ -1020,8 +1022,8 @@
     <row r="8" spans="1:13" ht="30" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="26"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
       <c r="E8" s="26"/>
       <c r="F8" s="26"/>
       <c r="G8" s="26"/>
@@ -1034,8 +1036,8 @@
     <row r="9" spans="1:13" ht="30" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="26"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
       <c r="E9" s="26"/>
       <c r="F9" s="26"/>
       <c r="G9" s="26"/>
@@ -1048,8 +1050,8 @@
     <row r="10" spans="1:13" ht="30" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="26"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
       <c r="E10" s="26"/>
       <c r="F10" s="26"/>
       <c r="G10" s="26"/>
@@ -1062,8 +1064,8 @@
     <row r="11" spans="1:13" ht="30" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="26"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
       <c r="E11" s="26"/>
       <c r="F11" s="26"/>
       <c r="G11" s="26"/>
@@ -1076,8 +1078,8 @@
     <row r="12" spans="1:13" ht="30" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="26"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
       <c r="E12" s="26"/>
       <c r="F12" s="26"/>
       <c r="G12" s="26"/>
@@ -1090,8 +1092,8 @@
     <row r="13" spans="1:13" ht="30" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="26"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
       <c r="E13" s="26"/>
       <c r="F13" s="26"/>
       <c r="G13" s="26"/>
@@ -1104,8 +1106,8 @@
     <row r="14" spans="1:13" ht="30" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="26"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
       <c r="E14" s="26"/>
       <c r="F14" s="26"/>
       <c r="G14" s="26"/>
@@ -1117,8 +1119,8 @@
     </row>
     <row r="15" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B15" s="26"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
       <c r="E15" s="26"/>
       <c r="F15" s="26"/>
       <c r="G15" s="26"/>
@@ -1130,8 +1132,8 @@
     </row>
     <row r="16" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B16" s="26"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
       <c r="E16" s="26"/>
       <c r="F16" s="26"/>
       <c r="G16" s="26"/>
@@ -1144,8 +1146,8 @@
     <row r="17" spans="1:12" ht="30" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="26"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
       <c r="E17" s="26"/>
       <c r="F17" s="26"/>
       <c r="G17" s="26"/>
@@ -1157,8 +1159,8 @@
     </row>
     <row r="18" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B18" s="26"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
       <c r="E18" s="26"/>
       <c r="F18" s="26"/>
       <c r="G18" s="26"/>
@@ -1170,8 +1172,8 @@
     </row>
     <row r="19" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B19" s="26"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
       <c r="E19" s="26"/>
       <c r="F19" s="26"/>
       <c r="G19" s="26"/>
@@ -1183,8 +1185,8 @@
     </row>
     <row r="20" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B20" s="26"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
       <c r="E20" s="26"/>
       <c r="F20" s="26"/>
       <c r="G20" s="26"/>
@@ -1196,8 +1198,8 @@
     </row>
     <row r="21" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B21" s="26"/>
-      <c r="C21" s="42"/>
-      <c r="D21" s="42"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
       <c r="E21" s="26"/>
       <c r="F21" s="26"/>
       <c r="G21" s="26"/>
@@ -1208,118 +1210,118 @@
       <c r="L21" s="26"/>
     </row>
     <row r="22" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="B22" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="30"/>
+      <c r="B22" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="48"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="40"/>
       <c r="G22" s="10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J22" s="5"/>
       <c r="K22" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L22" s="6"/>
     </row>
     <row r="23" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="B23" s="31"/>
-      <c r="C23" s="32"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="33"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="31"/>
       <c r="G23" s="7"/>
-      <c r="H23" s="50"/>
-      <c r="I23" s="35"/>
-      <c r="J23" s="35"/>
-      <c r="K23" s="35"/>
-      <c r="L23" s="36"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="36"/>
+      <c r="J23" s="36"/>
+      <c r="K23" s="36"/>
+      <c r="L23" s="37"/>
     </row>
     <row r="24" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
-      <c r="B24" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24" s="35"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="36"/>
-      <c r="H24" s="37"/>
-      <c r="I24" s="38"/>
-      <c r="J24" s="38"/>
-      <c r="K24" s="38"/>
-      <c r="L24" s="30"/>
+      <c r="B24" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="37"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="39"/>
+      <c r="L24" s="40"/>
     </row>
     <row r="25" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
-      <c r="B25" s="37"/>
-      <c r="C25" s="38"/>
-      <c r="D25" s="38"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="37"/>
-      <c r="I25" s="38"/>
-      <c r="J25" s="38"/>
-      <c r="K25" s="38"/>
-      <c r="L25" s="30"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="39"/>
+      <c r="K25" s="39"/>
+      <c r="L25" s="40"/>
     </row>
     <row r="26" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
-      <c r="B26" s="37"/>
-      <c r="C26" s="38"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="37"/>
-      <c r="I26" s="38"/>
-      <c r="J26" s="38"/>
-      <c r="K26" s="38"/>
-      <c r="L26" s="30"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="39"/>
+      <c r="K26" s="39"/>
+      <c r="L26" s="40"/>
     </row>
     <row r="27" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
-      <c r="B27" s="37"/>
-      <c r="C27" s="38"/>
-      <c r="D27" s="38"/>
-      <c r="E27" s="38"/>
-      <c r="F27" s="38"/>
-      <c r="G27" s="30"/>
-      <c r="H27" s="37"/>
-      <c r="I27" s="38"/>
-      <c r="J27" s="38"/>
-      <c r="K27" s="38"/>
-      <c r="L27" s="30"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="39"/>
+      <c r="K27" s="39"/>
+      <c r="L27" s="40"/>
     </row>
     <row r="28" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
-      <c r="B28" s="37"/>
-      <c r="C28" s="38"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="30"/>
-      <c r="H28" s="37"/>
-      <c r="I28" s="38"/>
-      <c r="J28" s="38"/>
-      <c r="K28" s="38"/>
-      <c r="L28" s="30"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="39"/>
+      <c r="J28" s="39"/>
+      <c r="K28" s="39"/>
+      <c r="L28" s="40"/>
     </row>
     <row r="29" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
-      <c r="B29" s="31"/>
-      <c r="C29" s="32"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="33"/>
-      <c r="H29" s="31"/>
-      <c r="I29" s="32"/>
-      <c r="J29" s="32"/>
-      <c r="K29" s="32"/>
-      <c r="L29" s="33"/>
+      <c r="B29" s="41"/>
+      <c r="C29" s="42"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="42"/>
+      <c r="F29" s="42"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="42"/>
+      <c r="J29" s="42"/>
+      <c r="K29" s="42"/>
+      <c r="L29" s="31"/>
     </row>
     <row r="30" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
       <c r="B30" s="8"/>
@@ -1355,6 +1357,18 @@
     <row r="38"/>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B22:F23"/>
+    <mergeCell ref="B24:G29"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="F1:J2"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:K5"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="C6:D6"/>
@@ -1371,18 +1385,6 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="C3:E3"/>
-    <mergeCell ref="B22:F23"/>
-    <mergeCell ref="B24:G29"/>
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="F1:J2"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:K5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/excel_payment.xlsx
+++ b/excel_payment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jackey\Desktop\github\work-order\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3177E884-5B65-41FC-B465-33C7D71D0C12}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0F7C536-1179-4ABB-A312-454F4FC999DF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView showHorizontalScroll="0" showSheetTabs="0" xWindow="32767" yWindow="32767" windowWidth="24180" windowHeight="13053" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,16 +23,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="27">
   <si>
     <t>彩意企業有限公司</t>
   </si>
   <si>
     <t>新北市新店區富貴街23巷2號1樓
 TEL:(02)-22145786 FAX:(02)2214-5782</t>
-  </si>
-  <si>
-    <t>報價單</t>
   </si>
   <si>
     <t>客戶名稱:</t>
@@ -111,6 +108,10 @@
   </si>
   <si>
     <t>備料計價</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>報價單</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -118,7 +119,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -188,6 +189,17 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="20"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -451,7 +463,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -522,21 +534,16 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
@@ -544,11 +551,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -559,25 +587,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -879,137 +901,137 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="33.700000000000003" customHeight="1" thickBot="1">
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
       <c r="E1" s="17"/>
-      <c r="F1" s="51" t="s">
+      <c r="F1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="34" t="s">
-        <v>2</v>
-      </c>
-      <c r="L1" s="29"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="L1" s="40"/>
     </row>
     <row r="2" spans="1:13" ht="17" customHeight="1">
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
       <c r="E2" s="20"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
     </row>
     <row r="3" spans="1:13" ht="32.700000000000003" customHeight="1">
       <c r="B3" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="50"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="27" t="s">
         <v>3</v>
-      </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="27" t="s">
-        <v>4</v>
       </c>
       <c r="G3" s="24"/>
       <c r="H3" s="21" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K3" s="22"/>
       <c r="L3" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="32.700000000000003" customHeight="1">
       <c r="B4" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="44"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="46"/>
+        <v>9</v>
+      </c>
+      <c r="C4" s="50"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="52"/>
       <c r="H4" s="23" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I4" s="22"/>
       <c r="J4" s="21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K4" s="22"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="28"/>
+      <c r="L4" s="46"/>
+      <c r="M4" s="45"/>
     </row>
     <row r="5" spans="1:13" ht="33" customHeight="1">
       <c r="B5" s="21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" s="22"/>
-      <c r="D5" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="52"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="53"/>
-      <c r="K5" s="53"/>
-      <c r="L5" s="31"/>
-      <c r="M5" s="29"/>
+      <c r="D5" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="43"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="44"/>
+      <c r="K5" s="44"/>
+      <c r="L5" s="33"/>
+      <c r="M5" s="40"/>
     </row>
     <row r="6" spans="1:13" ht="30" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="D6" s="48"/>
+      <c r="E6" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="33"/>
-      <c r="E6" s="13" t="s">
+      <c r="F6" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="G6" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="H6" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="15" t="s">
+      <c r="I6" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="J6" s="15" t="s">
+      <c r="K6" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="16" t="s">
-        <v>19</v>
-      </c>
       <c r="L6" s="25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="30" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="26"/>
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
       <c r="G7" s="26"/>
@@ -1022,8 +1044,8 @@
     <row r="8" spans="1:13" ht="30" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="26"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
       <c r="E8" s="26"/>
       <c r="F8" s="26"/>
       <c r="G8" s="26"/>
@@ -1036,8 +1058,8 @@
     <row r="9" spans="1:13" ht="30" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="26"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
       <c r="E9" s="26"/>
       <c r="F9" s="26"/>
       <c r="G9" s="26"/>
@@ -1050,8 +1072,8 @@
     <row r="10" spans="1:13" ht="30" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="26"/>
-      <c r="C10" s="43"/>
-      <c r="D10" s="43"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="42"/>
       <c r="E10" s="26"/>
       <c r="F10" s="26"/>
       <c r="G10" s="26"/>
@@ -1064,8 +1086,8 @@
     <row r="11" spans="1:13" ht="30" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="26"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
       <c r="E11" s="26"/>
       <c r="F11" s="26"/>
       <c r="G11" s="26"/>
@@ -1078,8 +1100,8 @@
     <row r="12" spans="1:13" ht="30" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="26"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
       <c r="E12" s="26"/>
       <c r="F12" s="26"/>
       <c r="G12" s="26"/>
@@ -1092,8 +1114,8 @@
     <row r="13" spans="1:13" ht="30" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="26"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
       <c r="E13" s="26"/>
       <c r="F13" s="26"/>
       <c r="G13" s="26"/>
@@ -1106,8 +1128,8 @@
     <row r="14" spans="1:13" ht="30" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="26"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
       <c r="E14" s="26"/>
       <c r="F14" s="26"/>
       <c r="G14" s="26"/>
@@ -1119,8 +1141,8 @@
     </row>
     <row r="15" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B15" s="26"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
       <c r="E15" s="26"/>
       <c r="F15" s="26"/>
       <c r="G15" s="26"/>
@@ -1132,8 +1154,8 @@
     </row>
     <row r="16" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B16" s="26"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
       <c r="E16" s="26"/>
       <c r="F16" s="26"/>
       <c r="G16" s="26"/>
@@ -1146,8 +1168,8 @@
     <row r="17" spans="1:12" ht="30" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="26"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
       <c r="E17" s="26"/>
       <c r="F17" s="26"/>
       <c r="G17" s="26"/>
@@ -1159,8 +1181,8 @@
     </row>
     <row r="18" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B18" s="26"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
       <c r="E18" s="26"/>
       <c r="F18" s="26"/>
       <c r="G18" s="26"/>
@@ -1172,8 +1194,8 @@
     </row>
     <row r="19" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B19" s="26"/>
-      <c r="C19" s="43"/>
-      <c r="D19" s="43"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
       <c r="E19" s="26"/>
       <c r="F19" s="26"/>
       <c r="G19" s="26"/>
@@ -1185,8 +1207,8 @@
     </row>
     <row r="20" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B20" s="26"/>
-      <c r="C20" s="43"/>
-      <c r="D20" s="43"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
       <c r="E20" s="26"/>
       <c r="F20" s="26"/>
       <c r="G20" s="26"/>
@@ -1198,8 +1220,8 @@
     </row>
     <row r="21" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B21" s="26"/>
-      <c r="C21" s="43"/>
-      <c r="D21" s="43"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
       <c r="E21" s="26"/>
       <c r="F21" s="26"/>
       <c r="G21" s="26"/>
@@ -1210,118 +1232,118 @@
       <c r="L21" s="26"/>
     </row>
     <row r="22" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="B22" s="47" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" s="48"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="40"/>
+      <c r="B22" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="30"/>
       <c r="G22" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J22" s="5"/>
       <c r="K22" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" s="6"/>
+    </row>
+    <row r="23" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
+      <c r="B23" s="31"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="53"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="54"/>
+      <c r="K23" s="54"/>
+      <c r="L23" s="55"/>
+    </row>
+    <row r="24" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
+      <c r="B24" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="L22" s="6"/>
-    </row>
-    <row r="23" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="B23" s="41"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="35"/>
-      <c r="I23" s="36"/>
-      <c r="J23" s="36"/>
-      <c r="K23" s="36"/>
-      <c r="L23" s="37"/>
-    </row>
-    <row r="24" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
-      <c r="B24" s="49" t="s">
-        <v>23</v>
-      </c>
-      <c r="C24" s="36"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="36"/>
-      <c r="G24" s="37"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="39"/>
-      <c r="J24" s="39"/>
-      <c r="K24" s="39"/>
-      <c r="L24" s="40"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="56"/>
+      <c r="I24" s="57"/>
+      <c r="J24" s="57"/>
+      <c r="K24" s="57"/>
+      <c r="L24" s="58"/>
     </row>
     <row r="25" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
-      <c r="B25" s="38"/>
-      <c r="C25" s="39"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="40"/>
-      <c r="H25" s="38"/>
-      <c r="I25" s="39"/>
-      <c r="J25" s="39"/>
-      <c r="K25" s="39"/>
-      <c r="L25" s="40"/>
+      <c r="B25" s="37"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="56"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="57"/>
+      <c r="K25" s="57"/>
+      <c r="L25" s="58"/>
     </row>
     <row r="26" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
-      <c r="B26" s="38"/>
-      <c r="C26" s="39"/>
-      <c r="D26" s="39"/>
-      <c r="E26" s="39"/>
-      <c r="F26" s="39"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="38"/>
-      <c r="I26" s="39"/>
-      <c r="J26" s="39"/>
-      <c r="K26" s="39"/>
-      <c r="L26" s="40"/>
+      <c r="B26" s="37"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="56"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="57"/>
+      <c r="K26" s="57"/>
+      <c r="L26" s="58"/>
     </row>
     <row r="27" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
-      <c r="B27" s="38"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="39"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="38"/>
-      <c r="I27" s="39"/>
-      <c r="J27" s="39"/>
-      <c r="K27" s="39"/>
-      <c r="L27" s="40"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="38"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="56"/>
+      <c r="I27" s="57"/>
+      <c r="J27" s="57"/>
+      <c r="K27" s="57"/>
+      <c r="L27" s="58"/>
     </row>
     <row r="28" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
-      <c r="B28" s="38"/>
-      <c r="C28" s="39"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="39"/>
-      <c r="J28" s="39"/>
-      <c r="K28" s="39"/>
-      <c r="L28" s="40"/>
+      <c r="B28" s="37"/>
+      <c r="C28" s="38"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="56"/>
+      <c r="I28" s="57"/>
+      <c r="J28" s="57"/>
+      <c r="K28" s="57"/>
+      <c r="L28" s="58"/>
     </row>
     <row r="29" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
-      <c r="B29" s="41"/>
-      <c r="C29" s="42"/>
-      <c r="D29" s="42"/>
-      <c r="E29" s="42"/>
-      <c r="F29" s="42"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="41"/>
-      <c r="I29" s="42"/>
-      <c r="J29" s="42"/>
-      <c r="K29" s="42"/>
-      <c r="L29" s="31"/>
+      <c r="B29" s="31"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="33"/>
+      <c r="H29" s="59"/>
+      <c r="I29" s="60"/>
+      <c r="J29" s="60"/>
+      <c r="K29" s="60"/>
+      <c r="L29" s="61"/>
     </row>
     <row r="30" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
       <c r="B30" s="8"/>
@@ -1357,18 +1379,6 @@
     <row r="38"/>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B22:F23"/>
-    <mergeCell ref="B24:G29"/>
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="F1:J2"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:K5"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="C6:D6"/>
@@ -1385,6 +1395,18 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="C3:E3"/>
+    <mergeCell ref="B22:F23"/>
+    <mergeCell ref="B24:G29"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="F1:J2"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:K5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/excel_payment.xlsx
+++ b/excel_payment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20388"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20390"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jackey\Desktop\github\work-order\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0F7C536-1179-4ABB-A312-454F4FC999DF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACA69195-7BB4-46D7-A806-AD102AA0DCAF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView showHorizontalScroll="0" showSheetTabs="0" xWindow="32767" yWindow="32767" windowWidth="24180" windowHeight="13053" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>彩意企業有限公司</t>
   </si>
@@ -534,6 +534,44 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -541,7 +579,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -554,52 +591,15 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -901,44 +901,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="33.700000000000003" customHeight="1" thickBot="1">
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
       <c r="E1" s="17"/>
-      <c r="F1" s="41" t="s">
+      <c r="F1" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="49" t="s">
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="40"/>
+      <c r="L1" s="29"/>
     </row>
     <row r="2" spans="1:13" ht="17" customHeight="1">
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
       <c r="E2" s="20"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
     </row>
     <row r="3" spans="1:13" ht="32.700000000000003" customHeight="1">
       <c r="B3" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="52"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="47"/>
       <c r="F3" s="27" t="s">
         <v>3</v>
       </c>
@@ -959,11 +959,11 @@
       <c r="B4" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="50"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="52"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="47"/>
       <c r="H4" s="23" t="s">
         <v>7</v>
       </c>
@@ -972,36 +972,36 @@
         <v>8</v>
       </c>
       <c r="K4" s="22"/>
-      <c r="L4" s="46"/>
-      <c r="M4" s="45"/>
+      <c r="L4" s="30"/>
+      <c r="M4" s="28"/>
     </row>
     <row r="5" spans="1:13" ht="33" customHeight="1">
       <c r="B5" s="21" t="s">
         <v>23</v>
       </c>
       <c r="C5" s="22"/>
-      <c r="D5" s="43" t="s">
+      <c r="D5" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="43"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="44"/>
-      <c r="K5" s="44"/>
-      <c r="L5" s="33"/>
-      <c r="M5" s="40"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="61"/>
+      <c r="L5" s="31"/>
+      <c r="M5" s="29"/>
     </row>
     <row r="6" spans="1:13" ht="30" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="47" t="s">
+      <c r="C6" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="48"/>
+      <c r="D6" s="33"/>
       <c r="E6" s="13" t="s">
         <v>13</v>
       </c>
@@ -1030,8 +1030,8 @@
     <row r="7" spans="1:13" ht="30" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="26"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
       <c r="G7" s="26"/>
@@ -1044,8 +1044,8 @@
     <row r="8" spans="1:13" ht="30" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="26"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
       <c r="E8" s="26"/>
       <c r="F8" s="26"/>
       <c r="G8" s="26"/>
@@ -1058,8 +1058,8 @@
     <row r="9" spans="1:13" ht="30" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="26"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
       <c r="E9" s="26"/>
       <c r="F9" s="26"/>
       <c r="G9" s="26"/>
@@ -1072,8 +1072,8 @@
     <row r="10" spans="1:13" ht="30" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="26"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
       <c r="E10" s="26"/>
       <c r="F10" s="26"/>
       <c r="G10" s="26"/>
@@ -1086,8 +1086,8 @@
     <row r="11" spans="1:13" ht="30" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="26"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
       <c r="E11" s="26"/>
       <c r="F11" s="26"/>
       <c r="G11" s="26"/>
@@ -1100,8 +1100,8 @@
     <row r="12" spans="1:13" ht="30" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="26"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
       <c r="E12" s="26"/>
       <c r="F12" s="26"/>
       <c r="G12" s="26"/>
@@ -1114,8 +1114,8 @@
     <row r="13" spans="1:13" ht="30" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="26"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
       <c r="E13" s="26"/>
       <c r="F13" s="26"/>
       <c r="G13" s="26"/>
@@ -1128,8 +1128,8 @@
     <row r="14" spans="1:13" ht="30" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="26"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
       <c r="E14" s="26"/>
       <c r="F14" s="26"/>
       <c r="G14" s="26"/>
@@ -1141,8 +1141,8 @@
     </row>
     <row r="15" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B15" s="26"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
       <c r="E15" s="26"/>
       <c r="F15" s="26"/>
       <c r="G15" s="26"/>
@@ -1154,8 +1154,8 @@
     </row>
     <row r="16" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B16" s="26"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
       <c r="E16" s="26"/>
       <c r="F16" s="26"/>
       <c r="G16" s="26"/>
@@ -1168,8 +1168,8 @@
     <row r="17" spans="1:12" ht="30" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="26"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
       <c r="E17" s="26"/>
       <c r="F17" s="26"/>
       <c r="G17" s="26"/>
@@ -1181,8 +1181,8 @@
     </row>
     <row r="18" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B18" s="26"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="44"/>
       <c r="E18" s="26"/>
       <c r="F18" s="26"/>
       <c r="G18" s="26"/>
@@ -1194,8 +1194,8 @@
     </row>
     <row r="19" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B19" s="26"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="44"/>
       <c r="E19" s="26"/>
       <c r="F19" s="26"/>
       <c r="G19" s="26"/>
@@ -1207,8 +1207,8 @@
     </row>
     <row r="20" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B20" s="26"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
       <c r="E20" s="26"/>
       <c r="F20" s="26"/>
       <c r="G20" s="26"/>
@@ -1220,8 +1220,8 @@
     </row>
     <row r="21" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B21" s="26"/>
-      <c r="C21" s="42"/>
-      <c r="D21" s="42"/>
+      <c r="C21" s="44"/>
+      <c r="D21" s="44"/>
       <c r="E21" s="26"/>
       <c r="F21" s="26"/>
       <c r="G21" s="26"/>
@@ -1232,13 +1232,13 @@
       <c r="L21" s="26"/>
     </row>
     <row r="22" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="B22" s="28" t="s">
+      <c r="B22" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="30"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="49"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="50"/>
       <c r="G22" s="10" t="s">
         <v>19</v>
       </c>
@@ -1253,97 +1253,97 @@
       <c r="L22" s="6"/>
     </row>
     <row r="23" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="B23" s="31"/>
-      <c r="C23" s="32"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="33"/>
+      <c r="B23" s="51"/>
+      <c r="C23" s="52"/>
+      <c r="D23" s="52"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="31"/>
       <c r="G23" s="7"/>
-      <c r="H23" s="53"/>
-      <c r="I23" s="54"/>
-      <c r="J23" s="54"/>
-      <c r="K23" s="54"/>
-      <c r="L23" s="55"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="36"/>
+      <c r="J23" s="36"/>
+      <c r="K23" s="36"/>
+      <c r="L23" s="37"/>
     </row>
     <row r="24" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
-      <c r="B24" s="34" t="s">
+      <c r="B24" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="35"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="36"/>
-      <c r="H24" s="56"/>
-      <c r="I24" s="57"/>
-      <c r="J24" s="57"/>
-      <c r="K24" s="57"/>
-      <c r="L24" s="58"/>
+      <c r="C24" s="54"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="55"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="39"/>
+      <c r="L24" s="40"/>
     </row>
     <row r="25" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
-      <c r="B25" s="37"/>
-      <c r="C25" s="38"/>
-      <c r="D25" s="38"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="56"/>
-      <c r="I25" s="57"/>
-      <c r="J25" s="57"/>
-      <c r="K25" s="57"/>
-      <c r="L25" s="58"/>
+      <c r="B25" s="56"/>
+      <c r="C25" s="57"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="57"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="50"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="39"/>
+      <c r="K25" s="39"/>
+      <c r="L25" s="40"/>
     </row>
     <row r="26" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
-      <c r="B26" s="37"/>
-      <c r="C26" s="38"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="56"/>
-      <c r="I26" s="57"/>
-      <c r="J26" s="57"/>
-      <c r="K26" s="57"/>
-      <c r="L26" s="58"/>
+      <c r="B26" s="56"/>
+      <c r="C26" s="57"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="50"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="39"/>
+      <c r="K26" s="39"/>
+      <c r="L26" s="40"/>
     </row>
     <row r="27" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
-      <c r="B27" s="37"/>
-      <c r="C27" s="38"/>
-      <c r="D27" s="38"/>
-      <c r="E27" s="38"/>
-      <c r="F27" s="38"/>
-      <c r="G27" s="30"/>
-      <c r="H27" s="56"/>
-      <c r="I27" s="57"/>
-      <c r="J27" s="57"/>
-      <c r="K27" s="57"/>
-      <c r="L27" s="58"/>
+      <c r="B27" s="56"/>
+      <c r="C27" s="57"/>
+      <c r="D27" s="57"/>
+      <c r="E27" s="57"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="50"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="39"/>
+      <c r="K27" s="39"/>
+      <c r="L27" s="40"/>
     </row>
     <row r="28" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
-      <c r="B28" s="37"/>
-      <c r="C28" s="38"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="30"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="57"/>
-      <c r="J28" s="57"/>
-      <c r="K28" s="57"/>
-      <c r="L28" s="58"/>
+      <c r="B28" s="56"/>
+      <c r="C28" s="57"/>
+      <c r="D28" s="57"/>
+      <c r="E28" s="57"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="50"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="39"/>
+      <c r="J28" s="39"/>
+      <c r="K28" s="39"/>
+      <c r="L28" s="40"/>
     </row>
     <row r="29" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
-      <c r="B29" s="31"/>
-      <c r="C29" s="32"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="33"/>
-      <c r="H29" s="59"/>
-      <c r="I29" s="60"/>
-      <c r="J29" s="60"/>
-      <c r="K29" s="60"/>
-      <c r="L29" s="61"/>
+      <c r="B29" s="51"/>
+      <c r="C29" s="52"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="52"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="42"/>
+      <c r="J29" s="42"/>
+      <c r="K29" s="42"/>
+      <c r="L29" s="43"/>
     </row>
     <row r="30" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
       <c r="B30" s="8"/>
@@ -1379,6 +1379,18 @@
     <row r="38"/>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B22:F23"/>
+    <mergeCell ref="B24:G29"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="F1:J2"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:K5"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="C6:D6"/>
@@ -1395,18 +1407,6 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="C3:E3"/>
-    <mergeCell ref="B22:F23"/>
-    <mergeCell ref="B24:G29"/>
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="F1:J2"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:K5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/excel_payment.xlsx
+++ b/excel_payment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20390"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jackey\Desktop\github\work-order\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACA69195-7BB4-46D7-A806-AD102AA0DCAF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C17C7EED-336D-4550-9BC7-FCBF119F9221}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView showHorizontalScroll="0" showSheetTabs="0" xWindow="32767" yWindow="32767" windowWidth="24180" windowHeight="13053" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -92,11 +92,6 @@
     <t>製作總價</t>
   </si>
   <si>
-    <t>匯款資料:
-銀行:合作金庫-永吉分行(銀行代號006)
-帳號:0969-717-059213             戶名:彩意企業有限公司</t>
-  </si>
-  <si>
     <t>公司統編:</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -112,6 +107,12 @@
   </si>
   <si>
     <t>報價單</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>匯款資料:
+銀行:合作金庫-松山分行(銀行代號006)
+帳號:0969-717-059213             戶名:彩意企業有限公司</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -534,12 +535,43 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -560,9 +592,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -570,34 +599,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -901,44 +902,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="33.700000000000003" customHeight="1" thickBot="1">
-      <c r="B1" s="58" t="s">
+      <c r="B1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
       <c r="E1" s="17"/>
-      <c r="F1" s="59" t="s">
+      <c r="F1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="L1" s="29"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1" s="40"/>
     </row>
     <row r="2" spans="1:13" ht="17" customHeight="1">
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
       <c r="E2" s="20"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
     </row>
     <row r="3" spans="1:13" ht="32.700000000000003" customHeight="1">
       <c r="B3" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="45"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="47"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="61"/>
       <c r="F3" s="27" t="s">
         <v>3</v>
       </c>
@@ -959,11 +960,11 @@
       <c r="B4" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="45"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="47"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="61"/>
       <c r="H4" s="23" t="s">
         <v>7</v>
       </c>
@@ -972,36 +973,36 @@
         <v>8</v>
       </c>
       <c r="K4" s="22"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="28"/>
+      <c r="L4" s="46"/>
+      <c r="M4" s="45"/>
     </row>
     <row r="5" spans="1:13" ht="33" customHeight="1">
       <c r="B5" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" s="22"/>
-      <c r="D5" s="60" t="s">
+      <c r="D5" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="60"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="61"/>
-      <c r="L5" s="31"/>
-      <c r="M5" s="29"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="44"/>
+      <c r="K5" s="44"/>
+      <c r="L5" s="33"/>
+      <c r="M5" s="40"/>
     </row>
     <row r="6" spans="1:13" ht="30" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="33"/>
+      <c r="D6" s="48"/>
       <c r="E6" s="13" t="s">
         <v>13</v>
       </c>
@@ -1024,14 +1025,14 @@
         <v>18</v>
       </c>
       <c r="L6" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="30" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="26"/>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
       <c r="G7" s="26"/>
@@ -1044,8 +1045,8 @@
     <row r="8" spans="1:13" ht="30" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="26"/>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
       <c r="E8" s="26"/>
       <c r="F8" s="26"/>
       <c r="G8" s="26"/>
@@ -1058,8 +1059,8 @@
     <row r="9" spans="1:13" ht="30" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="26"/>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
       <c r="E9" s="26"/>
       <c r="F9" s="26"/>
       <c r="G9" s="26"/>
@@ -1072,8 +1073,8 @@
     <row r="10" spans="1:13" ht="30" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="26"/>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="42"/>
       <c r="E10" s="26"/>
       <c r="F10" s="26"/>
       <c r="G10" s="26"/>
@@ -1086,8 +1087,8 @@
     <row r="11" spans="1:13" ht="30" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="26"/>
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
       <c r="E11" s="26"/>
       <c r="F11" s="26"/>
       <c r="G11" s="26"/>
@@ -1100,8 +1101,8 @@
     <row r="12" spans="1:13" ht="30" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="26"/>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
       <c r="E12" s="26"/>
       <c r="F12" s="26"/>
       <c r="G12" s="26"/>
@@ -1114,8 +1115,8 @@
     <row r="13" spans="1:13" ht="30" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="26"/>
-      <c r="C13" s="44"/>
-      <c r="D13" s="44"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
       <c r="E13" s="26"/>
       <c r="F13" s="26"/>
       <c r="G13" s="26"/>
@@ -1128,8 +1129,8 @@
     <row r="14" spans="1:13" ht="30" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="26"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
       <c r="E14" s="26"/>
       <c r="F14" s="26"/>
       <c r="G14" s="26"/>
@@ -1141,8 +1142,8 @@
     </row>
     <row r="15" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B15" s="26"/>
-      <c r="C15" s="44"/>
-      <c r="D15" s="44"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
       <c r="E15" s="26"/>
       <c r="F15" s="26"/>
       <c r="G15" s="26"/>
@@ -1154,8 +1155,8 @@
     </row>
     <row r="16" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B16" s="26"/>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
       <c r="E16" s="26"/>
       <c r="F16" s="26"/>
       <c r="G16" s="26"/>
@@ -1168,8 +1169,8 @@
     <row r="17" spans="1:12" ht="30" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="26"/>
-      <c r="C17" s="44"/>
-      <c r="D17" s="44"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
       <c r="E17" s="26"/>
       <c r="F17" s="26"/>
       <c r="G17" s="26"/>
@@ -1181,8 +1182,8 @@
     </row>
     <row r="18" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B18" s="26"/>
-      <c r="C18" s="44"/>
-      <c r="D18" s="44"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
       <c r="E18" s="26"/>
       <c r="F18" s="26"/>
       <c r="G18" s="26"/>
@@ -1194,8 +1195,8 @@
     </row>
     <row r="19" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B19" s="26"/>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
       <c r="E19" s="26"/>
       <c r="F19" s="26"/>
       <c r="G19" s="26"/>
@@ -1207,8 +1208,8 @@
     </row>
     <row r="20" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B20" s="26"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
       <c r="E20" s="26"/>
       <c r="F20" s="26"/>
       <c r="G20" s="26"/>
@@ -1220,8 +1221,8 @@
     </row>
     <row r="21" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B21" s="26"/>
-      <c r="C21" s="44"/>
-      <c r="D21" s="44"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
       <c r="E21" s="26"/>
       <c r="F21" s="26"/>
       <c r="G21" s="26"/>
@@ -1232,13 +1233,13 @@
       <c r="L21" s="26"/>
     </row>
     <row r="22" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="B22" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" s="49"/>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="50"/>
+      <c r="B22" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="30"/>
       <c r="G22" s="10" t="s">
         <v>19</v>
       </c>
@@ -1253,97 +1254,97 @@
       <c r="L22" s="6"/>
     </row>
     <row r="23" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="B23" s="51"/>
-      <c r="C23" s="52"/>
-      <c r="D23" s="52"/>
-      <c r="E23" s="52"/>
-      <c r="F23" s="31"/>
+      <c r="B23" s="31"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="33"/>
       <c r="G23" s="7"/>
-      <c r="H23" s="35"/>
-      <c r="I23" s="36"/>
-      <c r="J23" s="36"/>
-      <c r="K23" s="36"/>
-      <c r="L23" s="37"/>
+      <c r="H23" s="50"/>
+      <c r="I23" s="51"/>
+      <c r="J23" s="51"/>
+      <c r="K23" s="51"/>
+      <c r="L23" s="52"/>
     </row>
     <row r="24" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
-      <c r="B24" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" s="54"/>
-      <c r="D24" s="54"/>
-      <c r="E24" s="54"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="55"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="39"/>
-      <c r="J24" s="39"/>
-      <c r="K24" s="39"/>
-      <c r="L24" s="40"/>
+      <c r="B24" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="35"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="53"/>
+      <c r="I24" s="54"/>
+      <c r="J24" s="54"/>
+      <c r="K24" s="54"/>
+      <c r="L24" s="55"/>
     </row>
     <row r="25" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
-      <c r="B25" s="56"/>
-      <c r="C25" s="57"/>
-      <c r="D25" s="57"/>
-      <c r="E25" s="57"/>
-      <c r="F25" s="57"/>
-      <c r="G25" s="50"/>
-      <c r="H25" s="38"/>
-      <c r="I25" s="39"/>
-      <c r="J25" s="39"/>
-      <c r="K25" s="39"/>
-      <c r="L25" s="40"/>
+      <c r="B25" s="37"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="54"/>
+      <c r="J25" s="54"/>
+      <c r="K25" s="54"/>
+      <c r="L25" s="55"/>
     </row>
     <row r="26" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
-      <c r="B26" s="56"/>
-      <c r="C26" s="57"/>
-      <c r="D26" s="57"/>
-      <c r="E26" s="57"/>
-      <c r="F26" s="57"/>
-      <c r="G26" s="50"/>
-      <c r="H26" s="38"/>
-      <c r="I26" s="39"/>
-      <c r="J26" s="39"/>
-      <c r="K26" s="39"/>
-      <c r="L26" s="40"/>
+      <c r="B26" s="37"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="54"/>
+      <c r="K26" s="54"/>
+      <c r="L26" s="55"/>
     </row>
     <row r="27" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
-      <c r="B27" s="56"/>
-      <c r="C27" s="57"/>
-      <c r="D27" s="57"/>
-      <c r="E27" s="57"/>
-      <c r="F27" s="57"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="38"/>
-      <c r="I27" s="39"/>
-      <c r="J27" s="39"/>
-      <c r="K27" s="39"/>
-      <c r="L27" s="40"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="38"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="53"/>
+      <c r="I27" s="54"/>
+      <c r="J27" s="54"/>
+      <c r="K27" s="54"/>
+      <c r="L27" s="55"/>
     </row>
     <row r="28" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
-      <c r="B28" s="56"/>
-      <c r="C28" s="57"/>
-      <c r="D28" s="57"/>
-      <c r="E28" s="57"/>
-      <c r="F28" s="57"/>
-      <c r="G28" s="50"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="39"/>
-      <c r="J28" s="39"/>
-      <c r="K28" s="39"/>
-      <c r="L28" s="40"/>
+      <c r="B28" s="37"/>
+      <c r="C28" s="38"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="53"/>
+      <c r="I28" s="54"/>
+      <c r="J28" s="54"/>
+      <c r="K28" s="54"/>
+      <c r="L28" s="55"/>
     </row>
     <row r="29" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
-      <c r="B29" s="51"/>
-      <c r="C29" s="52"/>
-      <c r="D29" s="52"/>
-      <c r="E29" s="52"/>
-      <c r="F29" s="52"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="41"/>
-      <c r="I29" s="42"/>
-      <c r="J29" s="42"/>
-      <c r="K29" s="42"/>
-      <c r="L29" s="43"/>
+      <c r="B29" s="31"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="33"/>
+      <c r="H29" s="56"/>
+      <c r="I29" s="57"/>
+      <c r="J29" s="57"/>
+      <c r="K29" s="57"/>
+      <c r="L29" s="58"/>
     </row>
     <row r="30" spans="1:12" s="1" customFormat="1" ht="12.7" customHeight="1">
       <c r="B30" s="8"/>
@@ -1379,18 +1380,6 @@
     <row r="38"/>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B22:F23"/>
-    <mergeCell ref="B24:G29"/>
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="F1:J2"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:K5"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="C6:D6"/>
@@ -1407,6 +1396,18 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="C3:E3"/>
+    <mergeCell ref="B22:F23"/>
+    <mergeCell ref="B24:G29"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="F1:J2"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:K5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
